--- a/public/sap-reporting/expansion-150-downloads/EXT-PP14-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP14-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3df3b85290954c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Ra038f5786c384a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R43491a6b4fdc4f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R334d5742c9f44783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R12875ef88f9d46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R4dd353b3653d44d7"/>
   </x:sheets>
 </x:workbook>
 </file>
